--- a/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_AAC.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_AAC.xlsx
@@ -2409,7 +2409,11 @@
           <t>AAC_M._LOCKHART</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>323766</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>M. Lockhart</t>
@@ -3025,7 +3029,11 @@
           <t>AAC_M._LOCKHART</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>323766</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>M. Lockhart</t>
@@ -6115,7 +6123,11 @@
           <t>AAC_M._LOCKHART</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>323766</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>M. Lockhart</t>
@@ -9951,7 +9963,11 @@
           <t>AAC_M._LOCKHART</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>323766</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>M. Lockhart</t>
@@ -10437,7 +10453,11 @@
           <t>AAC_M._LOCKHART</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>323766</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>M. Lockhart</t>
